--- a/collections/irregular_verbs.xlsx
+++ b/collections/irregular_verbs.xlsx
@@ -1003,7 +1003,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>The old bridge bore the weight of the truck.</t>
+          <t>The old bridge bore the weight of the lorry.</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
